--- a/HerculanoHouzel_etal_2015/Herculano-Houze-2015-Mammalian Brains Are Made.xlsx
+++ b/HerculanoHouzel_etal_2015/Herculano-Houze-2015-Mammalian Brains Are Made.xlsx
@@ -38183,8 +38183,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -38453,7 +38453,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD6CC5CC-EBB8-4105-BD9E-C002A07536CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE4BCFD-B042-4D85-8266-4E3A345C1048}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
